--- a/outputs/llm/gemini/channel_results_051.xlsx
+++ b/outputs/llm/gemini/channel_results_051.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K170"/>
+  <dimension ref="A1:L170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,7 +469,12 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Unnamed: 0</t>
+          <t>ideology_group</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>populism_group</t>
         </is>
       </c>
     </row>
@@ -506,7 +511,16 @@
       <c r="J2" t="n">
         <v>0.2166666666666667</v>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -541,7 +555,16 @@
       <c r="J3" t="n">
         <v>0.2</v>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -576,7 +599,16 @@
       <c r="J4" t="n">
         <v>0.1730769230769231</v>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -611,7 +643,16 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -646,7 +687,16 @@
       <c r="J6" t="n">
         <v>0.02173913043478261</v>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -681,7 +731,16 @@
       <c r="J7" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -716,7 +775,16 @@
       <c r="J8" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -751,7 +819,16 @@
       <c r="J9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -786,7 +863,16 @@
       <c r="J10" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -821,7 +907,16 @@
       <c r="J11" t="n">
         <v>0.6166666666666667</v>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -856,7 +951,16 @@
       <c r="J12" t="n">
         <v>0.3</v>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -887,7 +991,16 @@
       <c r="J13" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -922,7 +1035,16 @@
       <c r="J14" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -957,7 +1079,16 @@
       <c r="J15" t="n">
         <v>0.1</v>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -992,7 +1123,16 @@
       <c r="J16" t="n">
         <v>0</v>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1167,16 @@
       <c r="J17" t="n">
         <v>0</v>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1062,7 +1211,16 @@
       <c r="J18" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1097,7 +1255,16 @@
       <c r="J19" t="n">
         <v>0.25</v>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1132,7 +1299,16 @@
       <c r="J20" t="n">
         <v>0.2962962962962963</v>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1167,7 +1343,16 @@
       <c r="J21" t="n">
         <v>0.52</v>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1202,7 +1387,16 @@
       <c r="J22" t="n">
         <v>0.3166666666666667</v>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1237,7 +1431,16 @@
       <c r="J23" t="n">
         <v>0.2333333333333333</v>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1272,7 +1475,16 @@
       <c r="J24" t="n">
         <v>0.1</v>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1307,7 +1519,16 @@
       <c r="J25" t="n">
         <v>0.1</v>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1342,7 +1563,16 @@
       <c r="J26" t="n">
         <v>0</v>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1377,7 +1607,16 @@
       <c r="J27" t="n">
         <v>0</v>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1412,7 +1651,16 @@
       <c r="J28" t="n">
         <v>0.5</v>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1447,7 +1695,16 @@
       <c r="J29" t="n">
         <v>0</v>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1482,7 +1739,16 @@
       <c r="J30" t="n">
         <v>0</v>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1517,7 +1783,16 @@
       <c r="J31" t="n">
         <v>0.25</v>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1552,7 +1827,16 @@
       <c r="J32" t="n">
         <v>0.3</v>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1587,7 +1871,16 @@
       <c r="J33" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1622,7 +1915,16 @@
       <c r="J34" t="n">
         <v>0</v>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1657,7 +1959,16 @@
       <c r="J35" t="n">
         <v>0.375</v>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1692,7 +2003,16 @@
       <c r="J36" t="n">
         <v>0.6610169491525424</v>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1727,7 +2047,16 @@
       <c r="J37" t="n">
         <v>0.4666666666666667</v>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1762,7 +2091,16 @@
       <c r="J38" t="n">
         <v>0.7833333333333333</v>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1797,7 +2135,16 @@
       <c r="J39" t="n">
         <v>0.25</v>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1832,7 +2179,16 @@
       <c r="J40" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1867,7 +2223,16 @@
       <c r="J41" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1902,7 +2267,16 @@
       <c r="J42" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1937,7 +2311,16 @@
       <c r="J43" t="n">
         <v>0</v>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1972,7 +2355,16 @@
       <c r="J44" t="n">
         <v>0</v>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2007,7 +2399,16 @@
       <c r="J45" t="n">
         <v>0.07894736842105263</v>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2042,7 +2443,16 @@
       <c r="J46" t="n">
         <v>0.2666666666666667</v>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2077,7 +2487,16 @@
       <c r="J47" t="n">
         <v>0.1166666666666667</v>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2112,7 +2531,16 @@
       <c r="J48" t="n">
         <v>0.8695652173913043</v>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2147,7 +2575,16 @@
       <c r="J49" t="n">
         <v>0.1162790697674419</v>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2182,7 +2619,16 @@
       <c r="J50" t="n">
         <v>0.2166666666666667</v>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2217,7 +2663,16 @@
       <c r="J51" t="n">
         <v>0.7</v>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2252,7 +2707,16 @@
       <c r="J52" t="n">
         <v>0</v>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2287,7 +2751,16 @@
       <c r="J53" t="n">
         <v>0.2333333333333333</v>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2311,6 +2784,7 @@
         <v>1</v>
       </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2345,7 +2819,16 @@
       <c r="J55" t="n">
         <v>0.25</v>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2380,7 +2863,16 @@
       <c r="J56" t="n">
         <v>0</v>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2415,7 +2907,16 @@
       <c r="J57" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2450,7 +2951,16 @@
       <c r="J58" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2485,7 +2995,16 @@
       <c r="J59" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2520,7 +3039,16 @@
       <c r="J60" t="n">
         <v>0.3636363636363636</v>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2555,7 +3083,16 @@
       <c r="J61" t="n">
         <v>0</v>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2579,6 +3116,7 @@
         <v>1</v>
       </c>
       <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2613,7 +3151,16 @@
       <c r="J63" t="n">
         <v>0.1833333333333333</v>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2648,7 +3195,16 @@
       <c r="J64" t="n">
         <v>0</v>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2683,7 +3239,16 @@
       <c r="J65" t="n">
         <v>0.03225806451612903</v>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2718,7 +3283,16 @@
       <c r="J66" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2753,7 +3327,16 @@
       <c r="J67" t="n">
         <v>0.3</v>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2788,7 +3371,16 @@
       <c r="J68" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2823,7 +3415,16 @@
       <c r="J69" t="n">
         <v>0.5</v>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2858,7 +3459,16 @@
       <c r="J70" t="n">
         <v>0</v>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2893,7 +3503,16 @@
       <c r="J71" t="n">
         <v>0.1739130434782609</v>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2928,7 +3547,16 @@
       <c r="J72" t="n">
         <v>0.6086956521739131</v>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2963,7 +3591,16 @@
       <c r="J73" t="n">
         <v>0</v>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2998,7 +3635,16 @@
       <c r="J74" t="n">
         <v>0.5666666666666667</v>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3033,7 +3679,16 @@
       <c r="J75" t="n">
         <v>0.75</v>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3068,7 +3723,16 @@
       <c r="J76" t="n">
         <v>0.4</v>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3103,7 +3767,16 @@
       <c r="J77" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3138,7 +3811,16 @@
       <c r="J78" t="n">
         <v>0.2333333333333333</v>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3173,7 +3855,16 @@
       <c r="J79" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3208,7 +3899,16 @@
       <c r="J80" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3243,7 +3943,16 @@
       <c r="J81" t="n">
         <v>0.7058823529411765</v>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3278,7 +3987,16 @@
       <c r="J82" t="n">
         <v>0.4385964912280702</v>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3313,7 +4031,16 @@
       <c r="J83" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3348,7 +4075,16 @@
       <c r="J84" t="n">
         <v>0.3666666666666666</v>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3383,7 +4119,16 @@
       <c r="J85" t="n">
         <v>0.2</v>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3418,7 +4163,16 @@
       <c r="J86" t="n">
         <v>0</v>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3453,7 +4207,16 @@
       <c r="J87" t="n">
         <v>0.2222222222222222</v>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3484,7 +4247,16 @@
       <c r="J88" t="n">
         <v>0.1833333333333333</v>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3519,7 +4291,16 @@
       <c r="J89" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3554,7 +4335,16 @@
       <c r="J90" t="n">
         <v>0.2307692307692308</v>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3589,7 +4379,16 @@
       <c r="J91" t="n">
         <v>0</v>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3624,7 +4423,16 @@
       <c r="J92" t="n">
         <v>0</v>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3659,7 +4467,16 @@
       <c r="J93" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3694,7 +4511,16 @@
       <c r="J94" t="n">
         <v>0.01666666666666667</v>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3718,6 +4544,7 @@
         <v>1</v>
       </c>
       <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3752,7 +4579,16 @@
       <c r="J96" t="n">
         <v>0</v>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3787,7 +4623,16 @@
       <c r="J97" t="n">
         <v>0.4814814814814815</v>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3822,7 +4667,16 @@
       <c r="J98" t="n">
         <v>0.5490196078431373</v>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3857,7 +4711,16 @@
       <c r="J99" t="n">
         <v>0.05</v>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3892,7 +4755,16 @@
       <c r="J100" t="n">
         <v>0.05882352941176471</v>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3927,7 +4799,16 @@
       <c r="J101" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3962,7 +4843,16 @@
       <c r="J102" t="n">
         <v>0.423728813559322</v>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3997,7 +4887,16 @@
       <c r="J103" t="n">
         <v>0.35</v>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4032,7 +4931,16 @@
       <c r="J104" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4067,7 +4975,16 @@
       <c r="J105" t="n">
         <v>0.2166666666666667</v>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4102,7 +5019,16 @@
       <c r="J106" t="n">
         <v>0</v>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4137,7 +5063,16 @@
       <c r="J107" t="n">
         <v>0.8833333333333333</v>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4172,7 +5107,16 @@
       <c r="J108" t="n">
         <v>0</v>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4207,7 +5151,16 @@
       <c r="J109" t="n">
         <v>0.4666666666666667</v>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4242,7 +5195,16 @@
       <c r="J110" t="n">
         <v>0.1730769230769231</v>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4272,6 +5234,11 @@
         <v>0.5</v>
       </c>
       <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4306,7 +5273,16 @@
       <c r="J112" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4341,7 +5317,16 @@
       <c r="J113" t="n">
         <v>0.6428571428571429</v>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4376,7 +5361,16 @@
       <c r="J114" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4411,7 +5405,16 @@
       <c r="J115" t="n">
         <v>0.15</v>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4446,8 +5449,15 @@
       <c r="J116" t="n">
         <v>0.04</v>
       </c>
-      <c r="K116" t="n">
-        <v>4</v>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -4483,8 +5493,15 @@
       <c r="J117" t="n">
         <v>0</v>
       </c>
-      <c r="K117" t="n">
-        <v>6</v>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -4520,8 +5537,15 @@
       <c r="J118" t="n">
         <v>0</v>
       </c>
-      <c r="K118" t="n">
-        <v>7</v>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -4557,8 +5581,15 @@
       <c r="J119" t="n">
         <v>0.08695652173913043</v>
       </c>
-      <c r="K119" t="n">
-        <v>9</v>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -4594,8 +5625,15 @@
       <c r="J120" t="n">
         <v>0</v>
       </c>
-      <c r="K120" t="n">
-        <v>15</v>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -4631,8 +5669,15 @@
       <c r="J121" t="n">
         <v>0</v>
       </c>
-      <c r="K121" t="n">
-        <v>18</v>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -4668,8 +5713,15 @@
       <c r="J122" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="K122" t="n">
-        <v>20</v>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -4705,8 +5757,15 @@
       <c r="J123" t="n">
         <v>0</v>
       </c>
-      <c r="K123" t="n">
-        <v>23</v>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -4742,8 +5801,15 @@
       <c r="J124" t="n">
         <v>0</v>
       </c>
-      <c r="K124" t="n">
-        <v>24</v>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -4779,8 +5845,15 @@
       <c r="J125" t="n">
         <v>0.08888888888888889</v>
       </c>
-      <c r="K125" t="n">
-        <v>27</v>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -4816,8 +5889,15 @@
       <c r="J126" t="n">
         <v>0.02173913043478261</v>
       </c>
-      <c r="K126" t="n">
-        <v>29</v>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -4853,8 +5933,15 @@
       <c r="J127" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="K127" t="n">
-        <v>31</v>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -4890,8 +5977,15 @@
       <c r="J128" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="K128" t="n">
-        <v>33</v>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -4927,8 +6021,15 @@
       <c r="J129" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="K129" t="n">
-        <v>35</v>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -4964,8 +6065,15 @@
       <c r="J130" t="n">
         <v>0.4615384615384616</v>
       </c>
-      <c r="K130" t="n">
-        <v>37</v>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -5001,8 +6109,15 @@
       <c r="J131" t="n">
         <v>0.6333333333333333</v>
       </c>
-      <c r="K131" t="n">
-        <v>40</v>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -5038,8 +6153,15 @@
       <c r="J132" t="n">
         <v>0</v>
       </c>
-      <c r="K132" t="n">
-        <v>41</v>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -5075,8 +6197,15 @@
       <c r="J133" t="n">
         <v>0.7</v>
       </c>
-      <c r="K133" t="n">
-        <v>42</v>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -5112,8 +6241,15 @@
       <c r="J134" t="n">
         <v>0.05</v>
       </c>
-      <c r="K134" t="n">
-        <v>46</v>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -5149,8 +6285,15 @@
       <c r="J135" t="n">
         <v>0.8166666666666667</v>
       </c>
-      <c r="K135" t="n">
-        <v>48</v>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -5186,8 +6329,15 @@
       <c r="J136" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="K136" t="n">
-        <v>49</v>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -5223,8 +6373,15 @@
       <c r="J137" t="n">
         <v>0</v>
       </c>
-      <c r="K137" t="n">
-        <v>50</v>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -5260,8 +6417,15 @@
       <c r="J138" t="n">
         <v>0</v>
       </c>
-      <c r="K138" t="n">
-        <v>51</v>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
       </c>
     </row>
     <row r="139">
@@ -5297,8 +6461,15 @@
       <c r="J139" t="n">
         <v>0.01666666666666667</v>
       </c>
-      <c r="K139" t="n">
-        <v>53</v>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -5334,8 +6505,15 @@
       <c r="J140" t="n">
         <v>0</v>
       </c>
-      <c r="K140" t="n">
-        <v>55</v>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
       </c>
     </row>
     <row r="141">
@@ -5371,8 +6549,15 @@
       <c r="J141" t="n">
         <v>0</v>
       </c>
-      <c r="K141" t="n">
-        <v>57</v>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -5396,9 +6581,8 @@
       <c r="J142" t="n">
         <v>1</v>
       </c>
-      <c r="K142" t="n">
-        <v>59</v>
-      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5433,8 +6617,15 @@
       <c r="J143" t="n">
         <v>0.9666666666666667</v>
       </c>
-      <c r="K143" t="n">
-        <v>60</v>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -5470,8 +6661,15 @@
       <c r="J144" t="n">
         <v>0.25</v>
       </c>
-      <c r="K144" t="n">
-        <v>61</v>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -5507,8 +6705,15 @@
       <c r="J145" t="n">
         <v>0.6530612244897959</v>
       </c>
-      <c r="K145" t="n">
-        <v>62</v>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -5544,8 +6749,15 @@
       <c r="J146" t="n">
         <v>0</v>
       </c>
-      <c r="K146" t="n">
-        <v>63</v>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -5569,9 +6781,8 @@
       <c r="J147" t="n">
         <v>1</v>
       </c>
-      <c r="K147" t="n">
-        <v>65</v>
-      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5606,8 +6817,15 @@
       <c r="J148" t="n">
         <v>0</v>
       </c>
-      <c r="K148" t="n">
-        <v>68</v>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="149">
@@ -5643,8 +6861,15 @@
       <c r="J149" t="n">
         <v>0.05172413793103448</v>
       </c>
-      <c r="K149" t="n">
-        <v>70</v>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -5680,8 +6905,15 @@
       <c r="J150" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="K150" t="n">
-        <v>71</v>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="151">
@@ -5717,8 +6949,15 @@
       <c r="J151" t="n">
         <v>0.1363636363636364</v>
       </c>
-      <c r="K151" t="n">
-        <v>72</v>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="152">
@@ -5754,8 +6993,15 @@
       <c r="J152" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="K152" t="n">
-        <v>73</v>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="153">
@@ -5787,8 +7033,15 @@
       <c r="J153" t="n">
         <v>0.4</v>
       </c>
-      <c r="K153" t="n">
-        <v>74</v>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="154">
@@ -5824,8 +7077,15 @@
       <c r="J154" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="K154" t="n">
-        <v>75</v>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -5861,8 +7121,15 @@
       <c r="J155" t="n">
         <v>0.1621621621621622</v>
       </c>
-      <c r="K155" t="n">
-        <v>76</v>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
       </c>
     </row>
     <row r="156">
@@ -5898,8 +7165,15 @@
       <c r="J156" t="n">
         <v>0.7096774193548387</v>
       </c>
-      <c r="K156" t="n">
-        <v>82</v>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
       </c>
     </row>
     <row r="157">
@@ -5935,8 +7209,15 @@
       <c r="J157" t="n">
         <v>0.2</v>
       </c>
-      <c r="K157" t="n">
-        <v>84</v>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
       </c>
     </row>
     <row r="158">
@@ -5972,8 +7253,15 @@
       <c r="J158" t="n">
         <v>0</v>
       </c>
-      <c r="K158" t="n">
-        <v>85</v>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -6009,8 +7297,15 @@
       <c r="J159" t="n">
         <v>0</v>
       </c>
-      <c r="K159" t="n">
-        <v>87</v>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
       </c>
     </row>
     <row r="160">
@@ -6046,8 +7341,15 @@
       <c r="J160" t="n">
         <v>0.24</v>
       </c>
-      <c r="K160" t="n">
-        <v>88</v>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
       </c>
     </row>
     <row r="161">
@@ -6083,8 +7385,15 @@
       <c r="J161" t="n">
         <v>0.1864406779661017</v>
       </c>
-      <c r="K161" t="n">
-        <v>89</v>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
       </c>
     </row>
     <row r="162">
@@ -6120,8 +7429,15 @@
       <c r="J162" t="n">
         <v>0.25</v>
       </c>
-      <c r="K162" t="n">
-        <v>91</v>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
       </c>
     </row>
     <row r="163">
@@ -6157,8 +7473,15 @@
       <c r="J163" t="n">
         <v>0</v>
       </c>
-      <c r="K163" t="n">
-        <v>96</v>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
       </c>
     </row>
     <row r="164">
@@ -6194,8 +7517,15 @@
       <c r="J164" t="n">
         <v>0.175</v>
       </c>
-      <c r="K164" t="n">
-        <v>97</v>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
       </c>
     </row>
     <row r="165">
@@ -6219,9 +7549,8 @@
       <c r="J165" t="n">
         <v>1</v>
       </c>
-      <c r="K165" t="n">
-        <v>98</v>
-      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6256,8 +7585,15 @@
       <c r="J166" t="n">
         <v>0.45</v>
       </c>
-      <c r="K166" t="n">
-        <v>100</v>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>right</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
       </c>
     </row>
     <row r="167">
@@ -6293,8 +7629,15 @@
       <c r="J167" t="n">
         <v>0</v>
       </c>
-      <c r="K167" t="n">
-        <v>101</v>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
       </c>
     </row>
     <row r="168">
@@ -6330,8 +7673,15 @@
       <c r="J168" t="n">
         <v>0</v>
       </c>
-      <c r="K168" t="n">
-        <v>104</v>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>moderate</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -6367,8 +7717,15 @@
       <c r="J169" t="n">
         <v>0.3783783783783784</v>
       </c>
-      <c r="K169" t="n">
-        <v>112</v>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
       </c>
     </row>
     <row r="170">
@@ -6404,8 +7761,15 @@
       <c r="J170" t="n">
         <v>0.85</v>
       </c>
-      <c r="K170" t="n">
-        <v>113</v>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/outputs/llm/gemini/channel_results_051.xlsx
+++ b/outputs/llm/gemini/channel_results_051.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L170"/>
+  <dimension ref="A1:K170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,37 +444,32 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>ideology_channel</t>
+          <t>total_videos</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>populism_channel</t>
+          <t>share_ideology_minus_1</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>total_videos</t>
+          <t>share_populism_minus_1</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>share_ideology_minus_1</t>
+          <t>ideology_group</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>share_populism_minus_1</t>
+          <t>populism_group</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>ideology_group</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>populism_group</t>
+          <t>subscribers</t>
         </is>
       </c>
     </row>
@@ -497,29 +492,26 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>5.086956521739131</v>
+        <v>60</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3404255319148936</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="H2" t="n">
-        <v>60</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.2333333333333333</v>
-      </c>
-      <c r="J2" t="n">
         <v>0.2166666666666667</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K2" t="n">
+        <v>133000</v>
       </c>
     </row>
     <row r="3">
@@ -541,29 +533,26 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>5.020833333333333</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>0.21875</v>
+        <v>0.2</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
-      </c>
-      <c r="I3" t="n">
         <v>0.2</v>
       </c>
-      <c r="J3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K3" t="n">
+        <v>435000</v>
       </c>
     </row>
     <row r="4">
@@ -585,29 +574,26 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>4.107142857142857</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6162790697674418</v>
+        <v>0.1923076923076923</v>
       </c>
       <c r="H4" t="n">
-        <v>52</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.1923076923076923</v>
-      </c>
-      <c r="J4" t="n">
         <v>0.1730769230769231</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K4" t="n">
+        <v>2700000</v>
       </c>
     </row>
     <row r="5">
@@ -629,29 +615,26 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>4.166666666666667</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>9</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K5" t="n">
+        <v>253000</v>
       </c>
     </row>
     <row r="6">
@@ -673,29 +656,26 @@
         <v>9.5</v>
       </c>
       <c r="F6" t="n">
-        <v>8.316666666666666</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
-        <v>9.004761904761905</v>
+        <v>0.02173913043478261</v>
       </c>
       <c r="H6" t="n">
-        <v>46</v>
-      </c>
-      <c r="I6" t="n">
         <v>0.02173913043478261</v>
       </c>
-      <c r="J6" t="n">
-        <v>0.02173913043478261</v>
-      </c>
-      <c r="K6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K6" t="n">
+        <v>190000</v>
       </c>
     </row>
     <row r="7">
@@ -717,29 +697,26 @@
         <v>8.5</v>
       </c>
       <c r="F7" t="n">
-        <v>7.646</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>7.95</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
-      </c>
-      <c r="I7" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="J7" t="n">
-        <v>0.03333333333333333</v>
-      </c>
-      <c r="K7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K7" t="n">
+        <v>139000</v>
       </c>
     </row>
     <row r="8">
@@ -761,29 +738,26 @@
         <v>9.5</v>
       </c>
       <c r="F8" t="n">
-        <v>8.5</v>
+        <v>30</v>
       </c>
       <c r="G8" t="n">
-        <v>9.205882352941176</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="H8" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="J8" t="n">
-        <v>0.03333333333333333</v>
-      </c>
-      <c r="K8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K8" t="n">
+        <v>563000</v>
       </c>
     </row>
     <row r="9">
@@ -805,29 +779,26 @@
         <v>8.5</v>
       </c>
       <c r="F9" t="n">
-        <v>7.954237288135594</v>
+        <v>60</v>
       </c>
       <c r="G9" t="n">
-        <v>8.020338983050847</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>60</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K9" t="n">
+        <v>623000</v>
       </c>
     </row>
     <row r="10">
@@ -849,29 +820,26 @@
         <v>8.5</v>
       </c>
       <c r="F10" t="n">
-        <v>3.5</v>
+        <v>21</v>
       </c>
       <c r="G10" t="n">
-        <v>6.5</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="H10" t="n">
-        <v>21</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="J10" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K10" t="n">
+        <v>187000</v>
       </c>
     </row>
     <row r="11">
@@ -893,29 +861,26 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>5.113636363636363</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3695652173913043</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="H11" t="n">
-        <v>60</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.6333333333333333</v>
-      </c>
-      <c r="J11" t="n">
         <v>0.6166666666666667</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K11" t="n">
+        <v>1780000</v>
       </c>
     </row>
     <row r="12">
@@ -937,29 +902,26 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>4.804761904761905</v>
+        <v>60</v>
       </c>
       <c r="G12" t="n">
-        <v>1.392857142857143</v>
+        <v>0.3</v>
       </c>
       <c r="H12" t="n">
-        <v>60</v>
-      </c>
-      <c r="I12" t="n">
         <v>0.3</v>
       </c>
-      <c r="J12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K12" t="n">
+        <v>548000</v>
       </c>
     </row>
     <row r="13">
@@ -980,26 +942,27 @@
       <c r="E13" t="n">
         <v>6.75</v>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>52</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.9230769230769231</v>
+      </c>
       <c r="H13" t="n">
-        <v>52</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.9230769230769231</v>
-      </c>
-      <c r="J13" t="n">
         <v>0.8461538461538461</v>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K13" t="n">
+        <v>229000</v>
       </c>
     </row>
     <row r="14">
@@ -1021,29 +984,26 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>4.823529411764706</v>
+        <v>51</v>
       </c>
       <c r="G14" t="n">
-        <v>2.058823529411764</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H14" t="n">
-        <v>51</v>
-      </c>
-      <c r="I14" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="J14" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K14" t="n">
+        <v>131000</v>
       </c>
     </row>
     <row r="15">
@@ -1065,29 +1025,26 @@
         <v>6.5</v>
       </c>
       <c r="F15" t="n">
-        <v>5.6875</v>
+        <v>10</v>
       </c>
       <c r="G15" t="n">
-        <v>5.6875</v>
+        <v>0.1</v>
       </c>
       <c r="H15" t="n">
-        <v>10</v>
-      </c>
-      <c r="I15" t="n">
         <v>0.1</v>
       </c>
-      <c r="J15" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K15" t="n">
+        <v>468000</v>
       </c>
     </row>
     <row r="16">
@@ -1109,29 +1066,26 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>3.785714285714286</v>
+        <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4642857142857143</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>14</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K16" t="n">
+        <v>65700</v>
       </c>
     </row>
     <row r="17">
@@ -1153,29 +1107,26 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K17" t="n">
+        <v>493000</v>
       </c>
     </row>
     <row r="18">
@@ -1197,29 +1148,26 @@
         <v>9.5</v>
       </c>
       <c r="F18" t="n">
-        <v>8.324390243902439</v>
+        <v>60</v>
       </c>
       <c r="G18" t="n">
-        <v>8.992682926829268</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H18" t="n">
-        <v>60</v>
-      </c>
-      <c r="I18" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="J18" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="K18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K18" t="n">
+        <v>583000</v>
       </c>
     </row>
     <row r="19">
@@ -1241,29 +1189,26 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>4.833333333333333</v>
+        <v>4</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.25</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
-      </c>
-      <c r="I19" t="n">
         <v>0.25</v>
       </c>
-      <c r="J19" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K19" t="n">
+        <v>216000</v>
       </c>
     </row>
     <row r="20">
@@ -1285,29 +1230,26 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>4.894736842105263</v>
+        <v>27</v>
       </c>
       <c r="G20" t="n">
-        <v>0.131578947368421</v>
+        <v>0.2962962962962963</v>
       </c>
       <c r="H20" t="n">
-        <v>27</v>
-      </c>
-      <c r="I20" t="n">
         <v>0.2962962962962963</v>
       </c>
-      <c r="J20" t="n">
-        <v>0.2962962962962963</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K20" t="n">
+        <v>163000</v>
       </c>
     </row>
     <row r="21">
@@ -1329,29 +1271,26 @@
         <v>3.25</v>
       </c>
       <c r="F21" t="n">
-        <v>5.75</v>
+        <v>25</v>
       </c>
       <c r="G21" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="H21" t="n">
-        <v>25</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J21" t="n">
         <v>0.52</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K21" t="n">
+        <v>108000</v>
       </c>
     </row>
     <row r="22">
@@ -1373,29 +1312,26 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>4.871794871794871</v>
+        <v>60</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6585365853658537</v>
+        <v>0.35</v>
       </c>
       <c r="H22" t="n">
-        <v>60</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="J22" t="n">
         <v>0.3166666666666667</v>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K22" t="n">
+        <v>2310000</v>
       </c>
     </row>
     <row r="23">
@@ -1417,29 +1353,26 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>4.422222222222222</v>
+        <v>60</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6444444444444445</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="H23" t="n">
-        <v>60</v>
-      </c>
-      <c r="I23" t="n">
         <v>0.2333333333333333</v>
       </c>
-      <c r="J23" t="n">
-        <v>0.2333333333333333</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K23" t="n">
+        <v>149000</v>
       </c>
     </row>
     <row r="24">
@@ -1461,29 +1394,26 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>4.925925925925926</v>
+        <v>60</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3611111111111111</v>
+        <v>0.1</v>
       </c>
       <c r="H24" t="n">
-        <v>60</v>
-      </c>
-      <c r="I24" t="n">
         <v>0.1</v>
       </c>
-      <c r="J24" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K24" t="n">
+        <v>240000</v>
       </c>
     </row>
     <row r="25">
@@ -1505,29 +1435,26 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>4.703703703703703</v>
+        <v>60</v>
       </c>
       <c r="G25" t="n">
-        <v>0.06481481481481481</v>
+        <v>0.1</v>
       </c>
       <c r="H25" t="n">
-        <v>60</v>
-      </c>
-      <c r="I25" t="n">
         <v>0.1</v>
       </c>
-      <c r="J25" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K25" t="n">
+        <v>1130000</v>
       </c>
     </row>
     <row r="26">
@@ -1549,29 +1476,26 @@
         <v>8.5</v>
       </c>
       <c r="F26" t="n">
-        <v>7.089285714285714</v>
+        <v>40</v>
       </c>
       <c r="G26" t="n">
-        <v>7.839285714285714</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>40</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K26" t="n">
+        <v>247000</v>
       </c>
     </row>
     <row r="27">
@@ -1593,29 +1517,26 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K27" t="n">
+        <v>379000</v>
       </c>
     </row>
     <row r="28">
@@ -1637,29 +1558,26 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G28" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="J28" t="n">
         <v>0.5</v>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K28" t="n">
+        <v>143000</v>
       </c>
     </row>
     <row r="29">
@@ -1681,29 +1599,26 @@
         <v>9</v>
       </c>
       <c r="F29" t="n">
-        <v>6.166666666666667</v>
+        <v>9</v>
       </c>
       <c r="G29" t="n">
-        <v>7.833333333333333</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>9</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K29" t="n">
+        <v>68000</v>
       </c>
     </row>
     <row r="30">
@@ -1725,29 +1640,26 @@
         <v>9</v>
       </c>
       <c r="F30" t="n">
-        <v>7.691176470588236</v>
+        <v>60</v>
       </c>
       <c r="G30" t="n">
-        <v>8.661764705882353</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>60</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I30" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K30" t="n">
+        <v>262000</v>
       </c>
     </row>
     <row r="31">
@@ -1769,29 +1681,26 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>5.329545454545454</v>
+        <v>60</v>
       </c>
       <c r="G31" t="n">
-        <v>1.284090909090909</v>
+        <v>0.25</v>
       </c>
       <c r="H31" t="n">
-        <v>60</v>
-      </c>
-      <c r="I31" t="n">
         <v>0.25</v>
       </c>
-      <c r="J31" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K31" t="n">
+        <v>358000</v>
       </c>
     </row>
     <row r="32">
@@ -1813,29 +1722,26 @@
         <v>7.75</v>
       </c>
       <c r="F32" t="n">
-        <v>7</v>
+        <v>60</v>
       </c>
       <c r="G32" t="n">
-        <v>7.524390243902439</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="H32" t="n">
-        <v>60</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="J32" t="n">
         <v>0.3</v>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K32" t="n">
+        <v>77100</v>
       </c>
     </row>
     <row r="33">
@@ -1857,29 +1763,26 @@
         <v>3.75</v>
       </c>
       <c r="F33" t="n">
-        <v>7.083333333333333</v>
+        <v>11</v>
       </c>
       <c r="G33" t="n">
-        <v>4</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="H33" t="n">
-        <v>11</v>
-      </c>
-      <c r="I33" t="n">
         <v>0.4545454545454545</v>
       </c>
-      <c r="J33" t="n">
-        <v>0.4545454545454545</v>
-      </c>
-      <c r="K33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K33" t="n">
+        <v>53400</v>
       </c>
     </row>
     <row r="34">
@@ -1901,29 +1804,26 @@
         <v>7</v>
       </c>
       <c r="F34" t="n">
-        <v>6.5</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K34" t="n">
+        <v>106000</v>
       </c>
     </row>
     <row r="35">
@@ -1945,29 +1845,26 @@
         <v>2.5</v>
       </c>
       <c r="F35" t="n">
-        <v>4.75</v>
+        <v>40</v>
       </c>
       <c r="G35" t="n">
-        <v>3.208333333333333</v>
+        <v>0.375</v>
       </c>
       <c r="H35" t="n">
-        <v>40</v>
-      </c>
-      <c r="I35" t="n">
         <v>0.375</v>
       </c>
-      <c r="J35" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K35" t="n">
+        <v>116000</v>
       </c>
     </row>
     <row r="36">
@@ -1989,29 +1886,26 @@
         <v>5</v>
       </c>
       <c r="F36" t="n">
-        <v>4.125</v>
+        <v>59</v>
       </c>
       <c r="G36" t="n">
-        <v>3.815789473684211</v>
+        <v>0.7966101694915254</v>
       </c>
       <c r="H36" t="n">
-        <v>59</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.7966101694915254</v>
-      </c>
-      <c r="J36" t="n">
         <v>0.6610169491525424</v>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K36" t="n">
+        <v>119000</v>
       </c>
     </row>
     <row r="37">
@@ -2033,29 +1927,26 @@
         <v>7.25</v>
       </c>
       <c r="F37" t="n">
-        <v>7.0625</v>
+        <v>60</v>
       </c>
       <c r="G37" t="n">
-        <v>6.661290322580645</v>
+        <v>0.6</v>
       </c>
       <c r="H37" t="n">
-        <v>60</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J37" t="n">
         <v>0.4666666666666667</v>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K37" t="n">
+        <v>816000</v>
       </c>
     </row>
     <row r="38">
@@ -2077,29 +1968,26 @@
         <v>6.5</v>
       </c>
       <c r="F38" t="n">
-        <v>7.5</v>
+        <v>60</v>
       </c>
       <c r="G38" t="n">
-        <v>4.833333333333333</v>
+        <v>0.8</v>
       </c>
       <c r="H38" t="n">
-        <v>60</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="J38" t="n">
         <v>0.7833333333333333</v>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K38" t="n">
+        <v>57200</v>
       </c>
     </row>
     <row r="39">
@@ -2121,29 +2009,26 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>4.962222222222223</v>
+        <v>60</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7888888888888889</v>
+        <v>0.25</v>
       </c>
       <c r="H39" t="n">
-        <v>60</v>
-      </c>
-      <c r="I39" t="n">
         <v>0.25</v>
       </c>
-      <c r="J39" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K39" t="n">
+        <v>166000</v>
       </c>
     </row>
     <row r="40">
@@ -2165,29 +2050,26 @@
         <v>8.4</v>
       </c>
       <c r="F40" t="n">
-        <v>7.664285714285714</v>
+        <v>26</v>
       </c>
       <c r="G40" t="n">
-        <v>7.771428571428571</v>
+        <v>0.1153846153846154</v>
       </c>
       <c r="H40" t="n">
-        <v>26</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.1153846153846154</v>
-      </c>
-      <c r="J40" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K40" t="n">
+        <v>424000</v>
       </c>
     </row>
     <row r="41">
@@ -2209,29 +2091,26 @@
         <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>6.75</v>
+        <v>24</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>0.75</v>
       </c>
       <c r="H41" t="n">
-        <v>24</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J41" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K41" t="n">
+        <v>86600</v>
       </c>
     </row>
     <row r="42">
@@ -2253,29 +2132,26 @@
         <v>0.5</v>
       </c>
       <c r="F42" t="n">
-        <v>7.4</v>
+        <v>56</v>
       </c>
       <c r="G42" t="n">
-        <v>2.0625</v>
+        <v>0.9107142857142857</v>
       </c>
       <c r="H42" t="n">
-        <v>56</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.9107142857142857</v>
-      </c>
-      <c r="J42" t="n">
         <v>0.8571428571428571</v>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K42" t="n">
+        <v>107000</v>
       </c>
     </row>
     <row r="43">
@@ -2297,29 +2173,26 @@
         <v>8.5</v>
       </c>
       <c r="F43" t="n">
-        <v>7.6875</v>
+        <v>9</v>
       </c>
       <c r="G43" t="n">
-        <v>7.25</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>9</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I43" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K43" t="n">
+        <v>213000</v>
       </c>
     </row>
     <row r="44">
@@ -2341,29 +2214,26 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>3.991489361702127</v>
+        <v>54</v>
       </c>
       <c r="G44" t="n">
-        <v>1.25531914893617</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>54</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K44" t="n">
+        <v>617000</v>
       </c>
     </row>
     <row r="45">
@@ -2385,29 +2255,26 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>7.26</v>
+        <v>38</v>
       </c>
       <c r="G45" t="n">
-        <v>2.519230769230769</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="H45" t="n">
-        <v>38</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0.1578947368421053</v>
-      </c>
-      <c r="J45" t="n">
         <v>0.07894736842105263</v>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K45" t="n">
+        <v>348000</v>
       </c>
     </row>
     <row r="46">
@@ -2429,29 +2296,26 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>5.048780487804878</v>
+        <v>60</v>
       </c>
       <c r="G46" t="n">
-        <v>1.068181818181818</v>
+        <v>0.3166666666666667</v>
       </c>
       <c r="H46" t="n">
-        <v>60</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.3166666666666667</v>
-      </c>
-      <c r="J46" t="n">
         <v>0.2666666666666667</v>
       </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K46" t="n">
+        <v>216000</v>
       </c>
     </row>
     <row r="47">
@@ -2473,29 +2337,26 @@
         <v>8.5</v>
       </c>
       <c r="F47" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="G47" t="n">
-        <v>9</v>
+        <v>0.3833333333333334</v>
       </c>
       <c r="H47" t="n">
-        <v>60</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.3833333333333334</v>
-      </c>
-      <c r="J47" t="n">
         <v>0.1166666666666667</v>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K47" t="n">
+        <v>102000</v>
       </c>
     </row>
     <row r="48">
@@ -2517,29 +2378,26 @@
         <v>7</v>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="G48" t="n">
-        <v>7</v>
+        <v>0.9565217391304348</v>
       </c>
       <c r="H48" t="n">
-        <v>23</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.9565217391304348</v>
-      </c>
-      <c r="J48" t="n">
         <v>0.8695652173913043</v>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K48" t="n">
+        <v>265000</v>
       </c>
     </row>
     <row r="49">
@@ -2561,29 +2419,26 @@
         <v>8.5</v>
       </c>
       <c r="F49" t="n">
-        <v>7.574193548387097</v>
+        <v>43</v>
       </c>
       <c r="G49" t="n">
-        <v>7.796774193548386</v>
+        <v>0.1395348837209302</v>
       </c>
       <c r="H49" t="n">
-        <v>43</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.1395348837209302</v>
-      </c>
-      <c r="J49" t="n">
         <v>0.1162790697674419</v>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K49" t="n">
+        <v>719000</v>
       </c>
     </row>
     <row r="50">
@@ -2605,29 +2460,26 @@
         <v>7</v>
       </c>
       <c r="F50" t="n">
-        <v>5.423076923076923</v>
+        <v>60</v>
       </c>
       <c r="G50" t="n">
-        <v>4.733333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="H50" t="n">
-        <v>60</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J50" t="n">
         <v>0.2166666666666667</v>
       </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K50" t="n">
+        <v>152000</v>
       </c>
     </row>
     <row r="51">
@@ -2649,29 +2501,26 @@
         <v>0.5</v>
       </c>
       <c r="F51" t="n">
-        <v>5.2</v>
+        <v>20</v>
       </c>
       <c r="G51" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="H51" t="n">
-        <v>20</v>
-      </c>
-      <c r="I51" t="n">
         <v>0.7</v>
       </c>
-      <c r="J51" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K51" t="n">
+        <v>167000</v>
       </c>
     </row>
     <row r="52">
@@ -2693,29 +2542,26 @@
         <v>3.5</v>
       </c>
       <c r="F52" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="G52" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>13</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I52" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K52" t="n">
+        <v>130000</v>
       </c>
     </row>
     <row r="53">
@@ -2737,29 +2583,26 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>5.052631578947368</v>
+        <v>60</v>
       </c>
       <c r="G53" t="n">
-        <v>0.275</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="H53" t="n">
-        <v>60</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="J53" t="n">
         <v>0.2333333333333333</v>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K53" t="n">
+        <v>68500</v>
       </c>
     </row>
     <row r="54">
@@ -2772,19 +2615,20 @@
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
+      <c r="F54" t="n">
+        <v>2</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
       <c r="H54" t="n">
-        <v>2</v>
-      </c>
-      <c r="I54" t="n">
         <v>1</v>
       </c>
-      <c r="J54" t="n">
-        <v>1</v>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="n">
+        <v>78700</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2805,29 +2649,26 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>4.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="G55" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="H55" t="n">
-        <v>4</v>
-      </c>
-      <c r="I55" t="n">
         <v>0.25</v>
       </c>
-      <c r="J55" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K55" t="n">
+        <v>133000</v>
       </c>
     </row>
     <row r="56">
@@ -2849,29 +2690,26 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>4.545454545454546</v>
+        <v>12</v>
       </c>
       <c r="G56" t="n">
-        <v>0.4090909090909091</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>12</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K56" t="n">
+        <v>2400000</v>
       </c>
     </row>
     <row r="57">
@@ -2893,29 +2731,26 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="H57" t="n">
-        <v>6</v>
-      </c>
-      <c r="I57" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="J57" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K57" t="n">
+        <v>1490000</v>
       </c>
     </row>
     <row r="58">
@@ -2937,29 +2772,26 @@
         <v>1.25</v>
       </c>
       <c r="F58" t="n">
-        <v>7.06</v>
+        <v>27</v>
       </c>
       <c r="G58" t="n">
-        <v>1.583333333333333</v>
+        <v>0.8148148148148148</v>
       </c>
       <c r="H58" t="n">
-        <v>27</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.8148148148148148</v>
-      </c>
-      <c r="J58" t="n">
         <v>0.7777777777777778</v>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K58" t="n">
+        <v>61200</v>
       </c>
     </row>
     <row r="59">
@@ -2981,29 +2813,26 @@
         <v>7.5</v>
       </c>
       <c r="F59" t="n">
-        <v>7.261904761904762</v>
+        <v>23</v>
       </c>
       <c r="G59" t="n">
-        <v>7</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="H59" t="n">
-        <v>23</v>
-      </c>
-      <c r="I59" t="n">
         <v>0.04347826086956522</v>
       </c>
-      <c r="J59" t="n">
-        <v>0.04347826086956522</v>
-      </c>
-      <c r="K59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K59" t="n">
+        <v>536000</v>
       </c>
     </row>
     <row r="60">
@@ -3025,29 +2854,26 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>4.785714285714286</v>
+        <v>11</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="H60" t="n">
-        <v>11</v>
-      </c>
-      <c r="I60" t="n">
         <v>0.3636363636363636</v>
       </c>
-      <c r="J60" t="n">
-        <v>0.3636363636363636</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K60" t="n">
+        <v>118000</v>
       </c>
     </row>
     <row r="61">
@@ -3069,29 +2895,26 @@
         <v>7.75</v>
       </c>
       <c r="F61" t="n">
-        <v>4.471698113207547</v>
+        <v>60</v>
       </c>
       <c r="G61" t="n">
-        <v>7.716981132075472</v>
+        <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>60</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K61" t="n">
+        <v>190000</v>
       </c>
     </row>
     <row r="62">
@@ -3104,19 +2927,20 @@
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
       <c r="H62" t="n">
         <v>1</v>
       </c>
-      <c r="I62" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" t="n">
-        <v>1</v>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="n">
+        <v>325000</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3137,29 +2961,26 @@
         <v>7</v>
       </c>
       <c r="F63" t="n">
-        <v>5.677777777777778</v>
+        <v>60</v>
       </c>
       <c r="G63" t="n">
-        <v>5.170212765957447</v>
+        <v>0.2166666666666667</v>
       </c>
       <c r="H63" t="n">
-        <v>60</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0.2166666666666667</v>
-      </c>
-      <c r="J63" t="n">
         <v>0.1833333333333333</v>
       </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K63" t="n">
+        <v>371000</v>
       </c>
     </row>
     <row r="64">
@@ -3181,29 +3002,26 @@
         <v>9</v>
       </c>
       <c r="F64" t="n">
-        <v>8.139215686274511</v>
+        <v>57</v>
       </c>
       <c r="G64" t="n">
-        <v>8.827450980392157</v>
+        <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>57</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I64" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K64" t="n">
+        <v>102000</v>
       </c>
     </row>
     <row r="65">
@@ -3225,29 +3043,26 @@
         <v>9.5</v>
       </c>
       <c r="F65" t="n">
-        <v>8.173076923076923</v>
+        <v>31</v>
       </c>
       <c r="G65" t="n">
-        <v>9.126923076923077</v>
+        <v>0.03225806451612903</v>
       </c>
       <c r="H65" t="n">
-        <v>31</v>
-      </c>
-      <c r="I65" t="n">
         <v>0.03225806451612903</v>
       </c>
-      <c r="J65" t="n">
-        <v>0.03225806451612903</v>
-      </c>
-      <c r="K65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K65" t="n">
+        <v>134000</v>
       </c>
     </row>
     <row r="66">
@@ -3269,29 +3084,26 @@
         <v>6.5</v>
       </c>
       <c r="F66" t="n">
-        <v>7.2</v>
+        <v>60</v>
       </c>
       <c r="G66" t="n">
-        <v>4.98</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="H66" t="n">
-        <v>60</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="J66" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K66" t="n">
+        <v>69700</v>
       </c>
     </row>
     <row r="67">
@@ -3313,29 +3125,26 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>3.857142857142857</v>
+        <v>10</v>
       </c>
       <c r="G67" t="n">
-        <v>1.142857142857143</v>
+        <v>0.3</v>
       </c>
       <c r="H67" t="n">
-        <v>10</v>
-      </c>
-      <c r="I67" t="n">
         <v>0.3</v>
       </c>
-      <c r="J67" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K67" t="n">
+        <v>127000</v>
       </c>
     </row>
     <row r="68">
@@ -3357,29 +3166,26 @@
         <v>6.75</v>
       </c>
       <c r="F68" t="n">
-        <v>6.3</v>
+        <v>13</v>
       </c>
       <c r="G68" t="n">
-        <v>5</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="H68" t="n">
-        <v>13</v>
-      </c>
-      <c r="I68" t="n">
         <v>0.07692307692307693</v>
       </c>
-      <c r="J68" t="n">
-        <v>0.07692307692307693</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K68" t="n">
+        <v>556000</v>
       </c>
     </row>
     <row r="69">
@@ -3401,29 +3207,26 @@
         <v>6.5</v>
       </c>
       <c r="F69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G69" t="n">
-        <v>6.5</v>
+        <v>0.5</v>
       </c>
       <c r="H69" t="n">
-        <v>4</v>
-      </c>
-      <c r="I69" t="n">
         <v>0.5</v>
       </c>
-      <c r="J69" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K69" t="n">
+        <v>168000</v>
       </c>
     </row>
     <row r="70">
@@ -3445,29 +3248,26 @@
         <v>8.5</v>
       </c>
       <c r="F70" t="n">
-        <v>7.346938775510204</v>
+        <v>60</v>
       </c>
       <c r="G70" t="n">
-        <v>6.928571428571429</v>
+        <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>60</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K70" t="n">
+        <v>122000</v>
       </c>
     </row>
     <row r="71">
@@ -3489,29 +3289,26 @@
         <v>8.5</v>
       </c>
       <c r="F71" t="n">
-        <v>6.375</v>
+        <v>46</v>
       </c>
       <c r="G71" t="n">
-        <v>7.902777777777778</v>
+        <v>0.1739130434782609</v>
       </c>
       <c r="H71" t="n">
-        <v>46</v>
-      </c>
-      <c r="I71" t="n">
         <v>0.1739130434782609</v>
       </c>
-      <c r="J71" t="n">
-        <v>0.1739130434782609</v>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K71" t="n">
+        <v>102000</v>
       </c>
     </row>
     <row r="72">
@@ -3533,29 +3330,26 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>7.333333333333333</v>
+        <v>23</v>
       </c>
       <c r="G72" t="n">
-        <v>2.388888888888889</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="H72" t="n">
-        <v>23</v>
-      </c>
-      <c r="I72" t="n">
         <v>0.6086956521739131</v>
       </c>
-      <c r="J72" t="n">
-        <v>0.6086956521739131</v>
-      </c>
-      <c r="K72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K72" t="n">
+        <v>82200</v>
       </c>
     </row>
     <row r="73">
@@ -3577,29 +3371,26 @@
         <v>7.5</v>
       </c>
       <c r="F73" t="n">
-        <v>7.527777777777778</v>
+        <v>60</v>
       </c>
       <c r="G73" t="n">
-        <v>7.287037037037037</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>60</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0</v>
-      </c>
-      <c r="K73" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I73" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K73" t="n">
+        <v>105000</v>
       </c>
     </row>
     <row r="74">
@@ -3621,29 +3412,26 @@
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>4.384615384615385</v>
+        <v>60</v>
       </c>
       <c r="G74" t="n">
-        <v>0.2115384615384615</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="H74" t="n">
-        <v>60</v>
-      </c>
-      <c r="I74" t="n">
         <v>0.5666666666666667</v>
       </c>
-      <c r="J74" t="n">
-        <v>0.5666666666666667</v>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K74" t="n">
+        <v>81600</v>
       </c>
     </row>
     <row r="75">
@@ -3665,29 +3453,26 @@
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>4.722222222222222</v>
+        <v>36</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="H75" t="n">
-        <v>36</v>
-      </c>
-      <c r="I75" t="n">
         <v>0.75</v>
       </c>
-      <c r="J75" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K75" t="n">
+        <v>77700</v>
       </c>
     </row>
     <row r="76">
@@ -3709,29 +3494,26 @@
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>4.675</v>
+        <v>15</v>
       </c>
       <c r="G76" t="n">
-        <v>0.3125</v>
+        <v>0.4</v>
       </c>
       <c r="H76" t="n">
-        <v>15</v>
-      </c>
-      <c r="I76" t="n">
         <v>0.4</v>
       </c>
-      <c r="J76" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K76" t="n">
+        <v>383000</v>
       </c>
     </row>
     <row r="77">
@@ -3753,29 +3535,26 @@
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="G77" t="n">
-        <v>2.7</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="H77" t="n">
-        <v>7</v>
-      </c>
-      <c r="I77" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="J77" t="n">
-        <v>0.1428571428571428</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K77" t="n">
+        <v>1300000</v>
       </c>
     </row>
     <row r="78">
@@ -3797,29 +3576,26 @@
         <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>5.340909090909091</v>
+        <v>30</v>
       </c>
       <c r="G78" t="n">
-        <v>3.543478260869565</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="H78" t="n">
-        <v>30</v>
-      </c>
-      <c r="I78" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="J78" t="n">
         <v>0.2333333333333333</v>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K78" t="n">
+        <v>280000</v>
       </c>
     </row>
     <row r="79">
@@ -3841,29 +3617,26 @@
         <v>9</v>
       </c>
       <c r="F79" t="n">
-        <v>7.782608695652174</v>
+        <v>60</v>
       </c>
       <c r="G79" t="n">
-        <v>8.720000000000001</v>
+        <v>0.1166666666666667</v>
       </c>
       <c r="H79" t="n">
-        <v>60</v>
-      </c>
-      <c r="I79" t="n">
-        <v>0.1166666666666667</v>
-      </c>
-      <c r="J79" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K79" t="n">
+        <v>170000</v>
       </c>
     </row>
     <row r="80">
@@ -3885,29 +3658,26 @@
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>5.01</v>
+        <v>60</v>
       </c>
       <c r="G80" t="n">
-        <v>0.14</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="H80" t="n">
-        <v>60</v>
-      </c>
-      <c r="I80" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="J80" t="n">
-        <v>0.1666666666666667</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K80" t="n">
+        <v>95000</v>
       </c>
     </row>
     <row r="81">
@@ -3929,29 +3699,26 @@
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>4.833333333333333</v>
+        <v>34</v>
       </c>
       <c r="G81" t="n">
-        <v>0.6111111111111112</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="H81" t="n">
-        <v>34</v>
-      </c>
-      <c r="I81" t="n">
         <v>0.7058823529411765</v>
       </c>
-      <c r="J81" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K81" t="n">
+        <v>137000</v>
       </c>
     </row>
     <row r="82">
@@ -3973,29 +3740,26 @@
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>4.316129032258065</v>
+        <v>57</v>
       </c>
       <c r="G82" t="n">
-        <v>0.8225806451612904</v>
+        <v>0.4385964912280702</v>
       </c>
       <c r="H82" t="n">
-        <v>57</v>
-      </c>
-      <c r="I82" t="n">
         <v>0.4385964912280702</v>
       </c>
-      <c r="J82" t="n">
-        <v>0.4385964912280702</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K82" t="n">
+        <v>67900</v>
       </c>
     </row>
     <row r="83">
@@ -4017,29 +3781,26 @@
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="H83" t="n">
-        <v>13</v>
-      </c>
-      <c r="I83" t="n">
         <v>0.6923076923076923</v>
       </c>
-      <c r="J83" t="n">
-        <v>0.6923076923076923</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K83" t="n">
+        <v>1400000</v>
       </c>
     </row>
     <row r="84">
@@ -4061,29 +3822,26 @@
         <v>7.5</v>
       </c>
       <c r="F84" t="n">
-        <v>6.172413793103448</v>
+        <v>60</v>
       </c>
       <c r="G84" t="n">
-        <v>6.483333333333333</v>
+        <v>0.3833333333333334</v>
       </c>
       <c r="H84" t="n">
-        <v>60</v>
-      </c>
-      <c r="I84" t="n">
-        <v>0.3833333333333334</v>
-      </c>
-      <c r="J84" t="n">
         <v>0.3666666666666666</v>
       </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K84" t="n">
+        <v>247000</v>
       </c>
     </row>
     <row r="85">
@@ -4105,29 +3863,26 @@
         <v>6.5</v>
       </c>
       <c r="F85" t="n">
-        <v>7.333333333333333</v>
+        <v>15</v>
       </c>
       <c r="G85" t="n">
-        <v>6.208333333333333</v>
+        <v>0.2</v>
       </c>
       <c r="H85" t="n">
-        <v>15</v>
-      </c>
-      <c r="I85" t="n">
         <v>0.2</v>
       </c>
-      <c r="J85" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K85" t="n">
+        <v>88400</v>
       </c>
     </row>
     <row r="86">
@@ -4149,29 +3904,26 @@
         <v>7.5</v>
       </c>
       <c r="F86" t="n">
-        <v>7.903389830508475</v>
+        <v>60</v>
       </c>
       <c r="G86" t="n">
-        <v>7.732203389830508</v>
+        <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>60</v>
-      </c>
-      <c r="I86" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" t="n">
-        <v>0</v>
-      </c>
-      <c r="K86" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I86" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K86" t="n">
+        <v>345000</v>
       </c>
     </row>
     <row r="87">
@@ -4193,29 +3945,26 @@
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>4.946428571428571</v>
+        <v>36</v>
       </c>
       <c r="G87" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="H87" t="n">
-        <v>36</v>
-      </c>
-      <c r="I87" t="n">
         <v>0.2222222222222222</v>
       </c>
-      <c r="J87" t="n">
-        <v>0.2222222222222222</v>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K87" t="n">
+        <v>184000</v>
       </c>
     </row>
     <row r="88">
@@ -4236,26 +3985,27 @@
       <c r="E88" t="n">
         <v>6</v>
       </c>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
+      <c r="F88" t="n">
+        <v>60</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.3333333333333333</v>
+      </c>
       <c r="H88" t="n">
-        <v>60</v>
-      </c>
-      <c r="I88" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="J88" t="n">
         <v>0.1833333333333333</v>
       </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K88" t="n">
+        <v>133000</v>
       </c>
     </row>
     <row r="89">
@@ -4277,29 +4027,26 @@
         <v>8.5</v>
       </c>
       <c r="F89" t="n">
-        <v>7.586956521739131</v>
+        <v>60</v>
       </c>
       <c r="G89" t="n">
-        <v>7.826086956521739</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="H89" t="n">
-        <v>60</v>
-      </c>
-      <c r="I89" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="J89" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="K89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K89" t="n">
+        <v>78400</v>
       </c>
     </row>
     <row r="90">
@@ -4321,29 +4068,26 @@
         <v>2</v>
       </c>
       <c r="F90" t="n">
-        <v>3.3125</v>
+        <v>13</v>
       </c>
       <c r="G90" t="n">
-        <v>3.3</v>
+        <v>0.3846153846153846</v>
       </c>
       <c r="H90" t="n">
-        <v>13</v>
-      </c>
-      <c r="I90" t="n">
-        <v>0.3846153846153846</v>
-      </c>
-      <c r="J90" t="n">
         <v>0.2307692307692308</v>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K90" t="n">
+        <v>166000</v>
       </c>
     </row>
     <row r="91">
@@ -4365,29 +4109,26 @@
         <v>8.5</v>
       </c>
       <c r="F91" t="n">
-        <v>7.894736842105263</v>
+        <v>60</v>
       </c>
       <c r="G91" t="n">
-        <v>8.342105263157896</v>
+        <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>60</v>
-      </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" t="n">
-        <v>0</v>
-      </c>
-      <c r="K91" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I91" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K91" t="n">
+        <v>489000</v>
       </c>
     </row>
     <row r="92">
@@ -4409,29 +4150,26 @@
         <v>3.5</v>
       </c>
       <c r="F92" t="n">
-        <v>6.1</v>
+        <v>15</v>
       </c>
       <c r="G92" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>15</v>
-      </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" t="n">
-        <v>0</v>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K92" t="n">
+        <v>125000</v>
       </c>
     </row>
     <row r="93">
@@ -4453,29 +4191,26 @@
         <v>3.25</v>
       </c>
       <c r="F93" t="n">
-        <v>3.625</v>
+        <v>14</v>
       </c>
       <c r="G93" t="n">
-        <v>3.5</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="H93" t="n">
-        <v>14</v>
-      </c>
-      <c r="I93" t="n">
         <v>0.4285714285714285</v>
       </c>
-      <c r="J93" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K93" t="n">
+        <v>1120000</v>
       </c>
     </row>
     <row r="94">
@@ -4497,29 +4232,26 @@
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>5.146551724137931</v>
+        <v>60</v>
       </c>
       <c r="G94" t="n">
-        <v>0.6982758620689655</v>
+        <v>0.01666666666666667</v>
       </c>
       <c r="H94" t="n">
-        <v>60</v>
-      </c>
-      <c r="I94" t="n">
         <v>0.01666666666666667</v>
       </c>
-      <c r="J94" t="n">
-        <v>0.01666666666666667</v>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K94" t="n">
+        <v>261000</v>
       </c>
     </row>
     <row r="95">
@@ -4532,19 +4264,20 @@
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
+      <c r="F95" t="n">
+        <v>24</v>
+      </c>
+      <c r="G95" t="n">
+        <v>1</v>
+      </c>
       <c r="H95" t="n">
-        <v>24</v>
-      </c>
-      <c r="I95" t="n">
         <v>1</v>
       </c>
-      <c r="J95" t="n">
-        <v>1</v>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="n">
+        <v>306000</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4565,29 +4298,26 @@
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="G96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>5</v>
-      </c>
-      <c r="I96" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="n">
-        <v>0</v>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K96" t="n">
+        <v>115000</v>
       </c>
     </row>
     <row r="97">
@@ -4609,29 +4339,26 @@
         <v>5.5</v>
       </c>
       <c r="F97" t="n">
-        <v>3.055555555555555</v>
+        <v>27</v>
       </c>
       <c r="G97" t="n">
-        <v>4</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="H97" t="n">
-        <v>27</v>
-      </c>
-      <c r="I97" t="n">
-        <v>0.5555555555555556</v>
-      </c>
-      <c r="J97" t="n">
         <v>0.4814814814814815</v>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K97" t="n">
+        <v>1450000</v>
       </c>
     </row>
     <row r="98">
@@ -4653,29 +4380,26 @@
         <v>7.5</v>
       </c>
       <c r="F98" t="n">
-        <v>4.428571428571429</v>
+        <v>51</v>
       </c>
       <c r="G98" t="n">
-        <v>6.022727272727272</v>
+        <v>0.5686274509803921</v>
       </c>
       <c r="H98" t="n">
-        <v>51</v>
-      </c>
-      <c r="I98" t="n">
-        <v>0.5686274509803921</v>
-      </c>
-      <c r="J98" t="n">
         <v>0.5490196078431373</v>
       </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K98" t="n">
+        <v>697000</v>
       </c>
     </row>
     <row r="99">
@@ -4697,29 +4421,26 @@
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>4.726415094339623</v>
+        <v>60</v>
       </c>
       <c r="G99" t="n">
-        <v>1.424528301886792</v>
+        <v>0.05</v>
       </c>
       <c r="H99" t="n">
-        <v>60</v>
-      </c>
-      <c r="I99" t="n">
         <v>0.05</v>
       </c>
-      <c r="J99" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K99" t="n">
+        <v>1810000</v>
       </c>
     </row>
     <row r="100">
@@ -4741,29 +4462,26 @@
         <v>0.75</v>
       </c>
       <c r="F100" t="n">
-        <v>4.4375</v>
+        <v>17</v>
       </c>
       <c r="G100" t="n">
-        <v>2.875</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="H100" t="n">
-        <v>17</v>
-      </c>
-      <c r="I100" t="n">
         <v>0.05882352941176471</v>
       </c>
-      <c r="J100" t="n">
-        <v>0.05882352941176471</v>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K100" t="n">
+        <v>772000</v>
       </c>
     </row>
     <row r="101">
@@ -4785,29 +4503,26 @@
         <v>8.25</v>
       </c>
       <c r="F101" t="n">
-        <v>3.107142857142857</v>
+        <v>45</v>
       </c>
       <c r="G101" t="n">
-        <v>7.879310344827586</v>
+        <v>0.3555555555555556</v>
       </c>
       <c r="H101" t="n">
-        <v>45</v>
-      </c>
-      <c r="I101" t="n">
-        <v>0.3555555555555556</v>
-      </c>
-      <c r="J101" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K101" t="n">
+        <v>173000</v>
       </c>
     </row>
     <row r="102">
@@ -4829,29 +4544,26 @@
         <v>4.75</v>
       </c>
       <c r="F102" t="n">
-        <v>6.7</v>
+        <v>59</v>
       </c>
       <c r="G102" t="n">
-        <v>4.303030303030303</v>
+        <v>0.4915254237288136</v>
       </c>
       <c r="H102" t="n">
-        <v>59</v>
-      </c>
-      <c r="I102" t="n">
-        <v>0.4915254237288136</v>
-      </c>
-      <c r="J102" t="n">
         <v>0.423728813559322</v>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K102" t="n">
+        <v>121000</v>
       </c>
     </row>
     <row r="103">
@@ -4873,29 +4585,26 @@
         <v>0</v>
       </c>
       <c r="F103" t="n">
-        <v>5.064102564102564</v>
+        <v>60</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="H103" t="n">
-        <v>60</v>
-      </c>
-      <c r="I103" t="n">
         <v>0.35</v>
       </c>
-      <c r="J103" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr">
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K103" t="n">
+        <v>289000</v>
       </c>
     </row>
     <row r="104">
@@ -4917,29 +4626,26 @@
         <v>0</v>
       </c>
       <c r="F104" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="H104" t="n">
-        <v>3</v>
-      </c>
-      <c r="I104" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="J104" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K104" t="n">
+        <v>246000</v>
       </c>
     </row>
     <row r="105">
@@ -4961,29 +4667,26 @@
         <v>0</v>
       </c>
       <c r="F105" t="n">
-        <v>4.815217391304348</v>
+        <v>60</v>
       </c>
       <c r="G105" t="n">
-        <v>0.4361702127659575</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="H105" t="n">
-        <v>60</v>
-      </c>
-      <c r="I105" t="n">
-        <v>0.2333333333333333</v>
-      </c>
-      <c r="J105" t="n">
         <v>0.2166666666666667</v>
       </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr">
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K105" t="n">
+        <v>324000</v>
       </c>
     </row>
     <row r="106">
@@ -5005,29 +4708,26 @@
         <v>0</v>
       </c>
       <c r="F106" t="n">
-        <v>4.111111111111111</v>
+        <v>11</v>
       </c>
       <c r="G106" t="n">
-        <v>1.45</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="H106" t="n">
-        <v>11</v>
-      </c>
-      <c r="I106" t="n">
-        <v>0.09090909090909091</v>
-      </c>
-      <c r="J106" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K106" t="n">
+        <v>218000</v>
       </c>
     </row>
     <row r="107">
@@ -5049,29 +4749,26 @@
         <v>0</v>
       </c>
       <c r="F107" t="n">
-        <v>4.833333333333333</v>
+        <v>60</v>
       </c>
       <c r="G107" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.8833333333333333</v>
       </c>
       <c r="H107" t="n">
-        <v>60</v>
-      </c>
-      <c r="I107" t="n">
         <v>0.8833333333333333</v>
       </c>
-      <c r="J107" t="n">
-        <v>0.8833333333333333</v>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr">
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K107" t="n">
+        <v>159000</v>
       </c>
     </row>
     <row r="108">
@@ -5093,29 +4790,26 @@
         <v>9</v>
       </c>
       <c r="F108" t="n">
-        <v>7.45925925925926</v>
+        <v>56</v>
       </c>
       <c r="G108" t="n">
-        <v>8.894444444444444</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>56</v>
-      </c>
-      <c r="I108" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I108" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K108" t="n">
+        <v>141000</v>
       </c>
     </row>
     <row r="109">
@@ -5137,29 +4831,26 @@
         <v>0</v>
       </c>
       <c r="F109" t="n">
-        <v>4.4375</v>
+        <v>15</v>
       </c>
       <c r="G109" t="n">
-        <v>0.8125</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="H109" t="n">
-        <v>15</v>
-      </c>
-      <c r="I109" t="n">
         <v>0.4666666666666667</v>
       </c>
-      <c r="J109" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K109" t="n">
+        <v>110000</v>
       </c>
     </row>
     <row r="110">
@@ -5181,29 +4872,26 @@
         <v>0</v>
       </c>
       <c r="F110" t="n">
-        <v>5.013513513513513</v>
+        <v>52</v>
       </c>
       <c r="G110" t="n">
-        <v>1.013513513513514</v>
+        <v>0.1730769230769231</v>
       </c>
       <c r="H110" t="n">
-        <v>52</v>
-      </c>
-      <c r="I110" t="n">
         <v>0.1730769230769231</v>
       </c>
-      <c r="J110" t="n">
-        <v>0.1730769230769231</v>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K110" t="n">
+        <v>411000</v>
       </c>
     </row>
     <row r="111">
@@ -5220,24 +4908,23 @@
       <c r="E111" t="n">
         <v>3.5</v>
       </c>
-      <c r="F111" t="inlineStr"/>
+      <c r="F111" t="n">
+        <v>4</v>
+      </c>
       <c r="G111" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="H111" t="n">
-        <v>4</v>
-      </c>
-      <c r="I111" t="n">
-        <v>1</v>
-      </c>
-      <c r="J111" t="n">
         <v>0.5</v>
       </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr">
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K111" t="n">
+        <v>565000</v>
       </c>
     </row>
     <row r="112">
@@ -5259,29 +4946,26 @@
         <v>0</v>
       </c>
       <c r="F112" t="n">
-        <v>5.110526315789474</v>
+        <v>60</v>
       </c>
       <c r="G112" t="n">
-        <v>2.052631578947369</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="H112" t="n">
-        <v>60</v>
-      </c>
-      <c r="I112" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="J112" t="n">
-        <v>0.03333333333333333</v>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K112" t="n">
+        <v>510000</v>
       </c>
     </row>
     <row r="113">
@@ -5303,29 +4987,26 @@
         <v>0</v>
       </c>
       <c r="F113" t="n">
-        <v>4.2</v>
+        <v>14</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="H113" t="n">
-        <v>14</v>
-      </c>
-      <c r="I113" t="n">
         <v>0.6428571428571429</v>
       </c>
-      <c r="J113" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K113" t="n">
+        <v>94600</v>
       </c>
     </row>
     <row r="114">
@@ -5347,29 +5028,26 @@
         <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>4.557692307692307</v>
+        <v>60</v>
       </c>
       <c r="G114" t="n">
-        <v>0.5480769230769231</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="H114" t="n">
-        <v>60</v>
-      </c>
-      <c r="I114" t="n">
         <v>0.1333333333333333</v>
       </c>
-      <c r="J114" t="n">
-        <v>0.1333333333333333</v>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K114" t="n">
+        <v>2150000</v>
       </c>
     </row>
     <row r="115">
@@ -5391,29 +5069,26 @@
         <v>2.5</v>
       </c>
       <c r="F115" t="n">
-        <v>5.51063829787234</v>
+        <v>60</v>
       </c>
       <c r="G115" t="n">
-        <v>3.255102040816327</v>
+        <v>0.1833333333333333</v>
       </c>
       <c r="H115" t="n">
-        <v>60</v>
-      </c>
-      <c r="I115" t="n">
-        <v>0.1833333333333333</v>
-      </c>
-      <c r="J115" t="n">
         <v>0.15</v>
       </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K115" t="n">
+        <v>245000</v>
       </c>
     </row>
     <row r="116">
@@ -5435,29 +5110,26 @@
         <v>9</v>
       </c>
       <c r="F116" t="n">
-        <v>8.585106382978724</v>
+        <v>50</v>
       </c>
       <c r="G116" t="n">
-        <v>8.51063829787234</v>
+        <v>0.04</v>
       </c>
       <c r="H116" t="n">
-        <v>50</v>
-      </c>
-      <c r="I116" t="n">
         <v>0.04</v>
       </c>
-      <c r="J116" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K116" t="inlineStr">
+      <c r="I116" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
+      <c r="J116" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K116" t="n">
+        <v>372000</v>
       </c>
     </row>
     <row r="117">
@@ -5479,29 +5151,26 @@
         <v>8</v>
       </c>
       <c r="F117" t="n">
-        <v>7.545454545454546</v>
+        <v>56</v>
       </c>
       <c r="G117" t="n">
-        <v>7.454545454545454</v>
+        <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>56</v>
-      </c>
-      <c r="I117" t="n">
-        <v>0</v>
-      </c>
-      <c r="J117" t="n">
-        <v>0</v>
-      </c>
-      <c r="K117" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I117" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
+      <c r="J117" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K117" t="n">
+        <v>168000</v>
       </c>
     </row>
     <row r="118">
@@ -5523,29 +5192,26 @@
         <v>8.5</v>
       </c>
       <c r="F118" t="n">
-        <v>7.172727272727273</v>
+        <v>60</v>
       </c>
       <c r="G118" t="n">
-        <v>7.259090909090909</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>60</v>
-      </c>
-      <c r="I118" t="n">
-        <v>0</v>
-      </c>
-      <c r="J118" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I118" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
+      <c r="J118" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K118" t="n">
+        <v>723000</v>
       </c>
     </row>
     <row r="119">
@@ -5567,29 +5233,26 @@
         <v>1</v>
       </c>
       <c r="F119" t="n">
-        <v>2.5</v>
+        <v>23</v>
       </c>
       <c r="G119" t="n">
-        <v>4.5</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="H119" t="n">
-        <v>23</v>
-      </c>
-      <c r="I119" t="n">
         <v>0.08695652173913043</v>
       </c>
-      <c r="J119" t="n">
-        <v>0.08695652173913043</v>
-      </c>
-      <c r="K119" t="inlineStr">
+      <c r="I119" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
+      <c r="J119" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K119" t="n">
+        <v>120000</v>
       </c>
     </row>
     <row r="120">
@@ -5611,29 +5274,26 @@
         <v>8.5</v>
       </c>
       <c r="F120" t="n">
-        <v>6.5</v>
+        <v>18</v>
       </c>
       <c r="G120" t="n">
-        <v>8.125</v>
+        <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>18</v>
-      </c>
-      <c r="I120" t="n">
-        <v>0</v>
-      </c>
-      <c r="J120" t="n">
-        <v>0</v>
-      </c>
-      <c r="K120" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I120" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
+      <c r="J120" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K120" t="n">
+        <v>189000</v>
       </c>
     </row>
     <row r="121">
@@ -5655,29 +5315,26 @@
         <v>9</v>
       </c>
       <c r="F121" t="n">
-        <v>7.413043478260869</v>
+        <v>60</v>
       </c>
       <c r="G121" t="n">
-        <v>8.391304347826088</v>
+        <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>60</v>
-      </c>
-      <c r="I121" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" t="n">
-        <v>0</v>
-      </c>
-      <c r="K121" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I121" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="J121" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K121" t="n">
+        <v>257000</v>
       </c>
     </row>
     <row r="122">
@@ -5699,29 +5356,26 @@
         <v>0</v>
       </c>
       <c r="F122" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="G122" t="n">
-        <v>1.625</v>
+        <v>0.95</v>
       </c>
       <c r="H122" t="n">
-        <v>60</v>
-      </c>
-      <c r="I122" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J122" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr">
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K122" t="n">
+        <v>649000</v>
       </c>
     </row>
     <row r="123">
@@ -5743,29 +5397,26 @@
         <v>0.5</v>
       </c>
       <c r="F123" t="n">
-        <v>3.611111111111111</v>
+        <v>10</v>
       </c>
       <c r="G123" t="n">
-        <v>2.055555555555555</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>10</v>
-      </c>
-      <c r="I123" t="n">
-        <v>0</v>
-      </c>
-      <c r="J123" t="n">
-        <v>0</v>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K123" t="n">
+        <v>341000</v>
       </c>
     </row>
     <row r="124">
@@ -5787,29 +5438,26 @@
         <v>8.5</v>
       </c>
       <c r="F124" t="n">
-        <v>7.70925925925926</v>
+        <v>60</v>
       </c>
       <c r="G124" t="n">
-        <v>7.327777777777778</v>
+        <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>60</v>
-      </c>
-      <c r="I124" t="n">
-        <v>0</v>
-      </c>
-      <c r="J124" t="n">
-        <v>0</v>
-      </c>
-      <c r="K124" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I124" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="J124" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K124" t="n">
+        <v>455000</v>
       </c>
     </row>
     <row r="125">
@@ -5831,29 +5479,26 @@
         <v>7</v>
       </c>
       <c r="F125" t="n">
-        <v>2.75</v>
+        <v>45</v>
       </c>
       <c r="G125" t="n">
-        <v>7.1875</v>
+        <v>0.08888888888888889</v>
       </c>
       <c r="H125" t="n">
-        <v>45</v>
-      </c>
-      <c r="I125" t="n">
         <v>0.08888888888888889</v>
       </c>
-      <c r="J125" t="n">
-        <v>0.08888888888888889</v>
-      </c>
-      <c r="K125" t="inlineStr">
+      <c r="I125" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr">
+      <c r="J125" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K125" t="n">
+        <v>103000</v>
       </c>
     </row>
     <row r="126">
@@ -5875,29 +5520,26 @@
         <v>9</v>
       </c>
       <c r="F126" t="n">
-        <v>6.5</v>
+        <v>46</v>
       </c>
       <c r="G126" t="n">
-        <v>5.972222222222222</v>
+        <v>0.04347826086956522</v>
       </c>
       <c r="H126" t="n">
-        <v>46</v>
-      </c>
-      <c r="I126" t="n">
-        <v>0.04347826086956522</v>
-      </c>
-      <c r="J126" t="n">
         <v>0.02173913043478261</v>
       </c>
-      <c r="K126" t="inlineStr">
+      <c r="I126" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr">
+      <c r="J126" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K126" t="n">
+        <v>122000</v>
       </c>
     </row>
     <row r="127">
@@ -5919,29 +5561,26 @@
         <v>6.25</v>
       </c>
       <c r="F127" t="n">
-        <v>4.766666666666667</v>
+        <v>60</v>
       </c>
       <c r="G127" t="n">
-        <v>4.192982456140351</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="H127" t="n">
-        <v>60</v>
-      </c>
-      <c r="I127" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="J127" t="n">
-        <v>0.03333333333333333</v>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L127" t="inlineStr">
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K127" t="n">
+        <v>194000</v>
       </c>
     </row>
     <row r="128">
@@ -5963,29 +5602,26 @@
         <v>8.5</v>
       </c>
       <c r="F128" t="n">
-        <v>8.364583333333334</v>
+        <v>60</v>
       </c>
       <c r="G128" t="n">
-        <v>8.166666666666666</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="H128" t="n">
-        <v>60</v>
-      </c>
-      <c r="I128" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="J128" t="n">
-        <v>0.03333333333333333</v>
-      </c>
-      <c r="K128" t="inlineStr">
+      <c r="I128" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr">
+      <c r="J128" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K128" t="n">
+        <v>382000</v>
       </c>
     </row>
     <row r="129">
@@ -6007,29 +5643,26 @@
         <v>7</v>
       </c>
       <c r="F129" t="n">
-        <v>1.173913043478261</v>
+        <v>24</v>
       </c>
       <c r="G129" t="n">
-        <v>6.043478260869565</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="H129" t="n">
-        <v>24</v>
-      </c>
-      <c r="I129" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="J129" t="n">
-        <v>0.04166666666666666</v>
-      </c>
-      <c r="K129" t="inlineStr">
+      <c r="I129" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr">
+      <c r="J129" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K129" t="n">
+        <v>172000</v>
       </c>
     </row>
     <row r="130">
@@ -6051,29 +5684,26 @@
         <v>7.5</v>
       </c>
       <c r="F130" t="n">
-        <v>8.03125</v>
+        <v>39</v>
       </c>
       <c r="G130" t="n">
-        <v>6.823529411764706</v>
+        <v>0.5128205128205128</v>
       </c>
       <c r="H130" t="n">
-        <v>39</v>
-      </c>
-      <c r="I130" t="n">
-        <v>0.5128205128205128</v>
-      </c>
-      <c r="J130" t="n">
         <v>0.4615384615384616</v>
       </c>
-      <c r="K130" t="inlineStr">
+      <c r="I130" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr">
+      <c r="J130" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K130" t="n">
+        <v>109000</v>
       </c>
     </row>
     <row r="131">
@@ -6095,29 +5725,26 @@
         <v>5</v>
       </c>
       <c r="F131" t="n">
-        <v>6.276190476190477</v>
+        <v>60</v>
       </c>
       <c r="G131" t="n">
-        <v>4.340909090909091</v>
+        <v>0.65</v>
       </c>
       <c r="H131" t="n">
-        <v>60</v>
-      </c>
-      <c r="I131" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="J131" t="n">
         <v>0.6333333333333333</v>
       </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L131" t="inlineStr">
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K131" t="n">
+        <v>105000</v>
       </c>
     </row>
     <row r="132">
@@ -6139,29 +5766,26 @@
         <v>8.5</v>
       </c>
       <c r="F132" t="n">
-        <v>7.078260869565218</v>
+        <v>23</v>
       </c>
       <c r="G132" t="n">
-        <v>8.456521739130435</v>
+        <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>23</v>
-      </c>
-      <c r="I132" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I132" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr">
+      <c r="J132" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K132" t="n">
+        <v>186000</v>
       </c>
     </row>
     <row r="133">
@@ -6183,29 +5807,26 @@
         <v>0</v>
       </c>
       <c r="F133" t="n">
-        <v>4.735294117647059</v>
+        <v>60</v>
       </c>
       <c r="G133" t="n">
-        <v>1.333333333333333</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="H133" t="n">
-        <v>60</v>
-      </c>
-      <c r="I133" t="n">
-        <v>0.7166666666666667</v>
-      </c>
-      <c r="J133" t="n">
         <v>0.7</v>
       </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L133" t="inlineStr">
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K133" t="n">
+        <v>3330000</v>
       </c>
     </row>
     <row r="134">
@@ -6227,29 +5848,26 @@
         <v>9</v>
       </c>
       <c r="F134" t="n">
-        <v>8.221951219512196</v>
+        <v>60</v>
       </c>
       <c r="G134" t="n">
-        <v>8.717073170731707</v>
+        <v>0.05</v>
       </c>
       <c r="H134" t="n">
-        <v>60</v>
-      </c>
-      <c r="I134" t="n">
         <v>0.05</v>
       </c>
-      <c r="J134" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="K134" t="inlineStr">
+      <c r="I134" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
+      <c r="J134" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K134" t="n">
+        <v>173000</v>
       </c>
     </row>
     <row r="135">
@@ -6271,29 +5889,26 @@
         <v>0</v>
       </c>
       <c r="F135" t="n">
-        <v>4.68</v>
+        <v>60</v>
       </c>
       <c r="G135" t="n">
-        <v>0.8</v>
+        <v>0.8166666666666667</v>
       </c>
       <c r="H135" t="n">
-        <v>60</v>
-      </c>
-      <c r="I135" t="n">
         <v>0.8166666666666667</v>
       </c>
-      <c r="J135" t="n">
-        <v>0.8166666666666667</v>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K135" t="n">
+        <v>658000</v>
       </c>
     </row>
     <row r="136">
@@ -6315,29 +5930,26 @@
         <v>3.5</v>
       </c>
       <c r="F136" t="n">
-        <v>3.818181818181818</v>
+        <v>14</v>
       </c>
       <c r="G136" t="n">
-        <v>3.45</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="H136" t="n">
-        <v>14</v>
-      </c>
-      <c r="I136" t="n">
-        <v>0.07142857142857142</v>
-      </c>
-      <c r="J136" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L136" t="inlineStr">
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K136" t="n">
+        <v>167000</v>
       </c>
     </row>
     <row r="137">
@@ -6359,29 +5971,26 @@
         <v>8.5</v>
       </c>
       <c r="F137" t="n">
-        <v>7.613636363636363</v>
+        <v>27</v>
       </c>
       <c r="G137" t="n">
-        <v>7.68</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="H137" t="n">
-        <v>27</v>
-      </c>
-      <c r="I137" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="J137" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I137" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
+      <c r="J137" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K137" t="n">
+        <v>288000</v>
       </c>
     </row>
     <row r="138">
@@ -6403,29 +6012,26 @@
         <v>7.75</v>
       </c>
       <c r="F138" t="n">
-        <v>6.691666666666666</v>
+        <v>12</v>
       </c>
       <c r="G138" t="n">
-        <v>6.958333333333333</v>
+        <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>12</v>
-      </c>
-      <c r="I138" t="n">
-        <v>0</v>
-      </c>
-      <c r="J138" t="n">
-        <v>0</v>
-      </c>
-      <c r="K138" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I138" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
+      <c r="J138" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K138" t="n">
+        <v>334000</v>
       </c>
     </row>
     <row r="139">
@@ -6447,29 +6053,26 @@
         <v>8.5</v>
       </c>
       <c r="F139" t="n">
-        <v>7.590566037735849</v>
+        <v>60</v>
       </c>
       <c r="G139" t="n">
-        <v>8.20188679245283</v>
+        <v>0.01666666666666667</v>
       </c>
       <c r="H139" t="n">
-        <v>60</v>
-      </c>
-      <c r="I139" t="n">
         <v>0.01666666666666667</v>
       </c>
-      <c r="J139" t="n">
-        <v>0.01666666666666667</v>
-      </c>
-      <c r="K139" t="inlineStr">
+      <c r="I139" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
+      <c r="J139" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K139" t="n">
+        <v>499000</v>
       </c>
     </row>
     <row r="140">
@@ -6491,29 +6094,26 @@
         <v>2</v>
       </c>
       <c r="F140" t="n">
-        <v>4.257142857142857</v>
+        <v>37</v>
       </c>
       <c r="G140" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>37</v>
-      </c>
-      <c r="I140" t="n">
-        <v>0</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0</v>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L140" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K140" t="n">
+        <v>109000</v>
       </c>
     </row>
     <row r="141">
@@ -6535,29 +6135,26 @@
         <v>8.5</v>
       </c>
       <c r="F141" t="n">
-        <v>7.75</v>
+        <v>13</v>
       </c>
       <c r="G141" t="n">
-        <v>8.5625</v>
+        <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>13</v>
-      </c>
-      <c r="I141" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" t="n">
-        <v>0</v>
-      </c>
-      <c r="K141" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I141" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
+      <c r="J141" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K141" t="n">
+        <v>267000</v>
       </c>
     </row>
     <row r="142">
@@ -6570,19 +6167,20 @@
       <c r="C142" t="inlineStr"/>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr"/>
-      <c r="G142" t="inlineStr"/>
+      <c r="F142" t="n">
+        <v>22</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1</v>
+      </c>
       <c r="H142" t="n">
-        <v>22</v>
-      </c>
-      <c r="I142" t="n">
         <v>1</v>
       </c>
-      <c r="J142" t="n">
-        <v>1</v>
-      </c>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="n">
+        <v>229000</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6603,29 +6201,26 @@
         <v>3</v>
       </c>
       <c r="F143" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="G143" t="n">
-        <v>3</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="H143" t="n">
-        <v>60</v>
-      </c>
-      <c r="I143" t="n">
         <v>0.9666666666666667</v>
       </c>
-      <c r="J143" t="n">
-        <v>0.9666666666666667</v>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K143" t="n">
+        <v>366000</v>
       </c>
     </row>
     <row r="144">
@@ -6647,29 +6242,26 @@
         <v>6</v>
       </c>
       <c r="F144" t="n">
-        <v>6.751515151515152</v>
+        <v>48</v>
       </c>
       <c r="G144" t="n">
-        <v>4.528571428571428</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="H144" t="n">
-        <v>48</v>
-      </c>
-      <c r="I144" t="n">
-        <v>0.2916666666666667</v>
-      </c>
-      <c r="J144" t="n">
         <v>0.25</v>
       </c>
-      <c r="K144" t="inlineStr">
+      <c r="I144" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
+      <c r="J144" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K144" t="n">
+        <v>294000</v>
       </c>
     </row>
     <row r="145">
@@ -6691,29 +6283,26 @@
         <v>0</v>
       </c>
       <c r="F145" t="n">
-        <v>4.705882352941177</v>
+        <v>49</v>
       </c>
       <c r="G145" t="n">
-        <v>1.941176470588235</v>
+        <v>0.6530612244897959</v>
       </c>
       <c r="H145" t="n">
-        <v>49</v>
-      </c>
-      <c r="I145" t="n">
         <v>0.6530612244897959</v>
       </c>
-      <c r="J145" t="n">
-        <v>0.6530612244897959</v>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L145" t="inlineStr">
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K145" t="n">
+        <v>75200</v>
       </c>
     </row>
     <row r="146">
@@ -6735,29 +6324,26 @@
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>16</v>
-      </c>
-      <c r="I146" t="n">
-        <v>0</v>
-      </c>
-      <c r="J146" t="n">
-        <v>0</v>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K146" t="n">
+        <v>105000</v>
       </c>
     </row>
     <row r="147">
@@ -6770,19 +6356,20 @@
       <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
+      <c r="F147" t="n">
+        <v>14</v>
+      </c>
+      <c r="G147" t="n">
+        <v>1</v>
+      </c>
       <c r="H147" t="n">
-        <v>14</v>
-      </c>
-      <c r="I147" t="n">
         <v>1</v>
       </c>
-      <c r="J147" t="n">
-        <v>1</v>
-      </c>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="n">
+        <v>137000</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6803,29 +6390,26 @@
         <v>8.25</v>
       </c>
       <c r="F148" t="n">
-        <v>7.34375</v>
+        <v>60</v>
       </c>
       <c r="G148" t="n">
-        <v>7.453125</v>
+        <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>60</v>
-      </c>
-      <c r="I148" t="n">
-        <v>0</v>
-      </c>
-      <c r="J148" t="n">
-        <v>0</v>
-      </c>
-      <c r="K148" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I148" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
+      <c r="J148" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K148" t="n">
+        <v>314000</v>
       </c>
     </row>
     <row r="149">
@@ -6847,29 +6431,26 @@
         <v>7</v>
       </c>
       <c r="F149" t="n">
-        <v>6.772727272727272</v>
+        <v>58</v>
       </c>
       <c r="G149" t="n">
-        <v>5.645833333333333</v>
+        <v>0.103448275862069</v>
       </c>
       <c r="H149" t="n">
-        <v>58</v>
-      </c>
-      <c r="I149" t="n">
-        <v>0.103448275862069</v>
-      </c>
-      <c r="J149" t="n">
         <v>0.05172413793103448</v>
       </c>
-      <c r="K149" t="inlineStr">
+      <c r="I149" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr">
+      <c r="J149" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K149" t="n">
+        <v>141000</v>
       </c>
     </row>
     <row r="150">
@@ -6891,29 +6472,26 @@
         <v>9</v>
       </c>
       <c r="F150" t="n">
-        <v>7.76</v>
+        <v>30</v>
       </c>
       <c r="G150" t="n">
-        <v>7.923076923076923</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="H150" t="n">
-        <v>30</v>
-      </c>
-      <c r="I150" t="n">
-        <v>0.06666666666666667</v>
-      </c>
-      <c r="J150" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="K150" t="inlineStr">
+      <c r="I150" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr">
+      <c r="J150" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K150" t="n">
+        <v>323000</v>
       </c>
     </row>
     <row r="151">
@@ -6935,29 +6513,26 @@
         <v>9</v>
       </c>
       <c r="F151" t="n">
-        <v>8.5</v>
+        <v>22</v>
       </c>
       <c r="G151" t="n">
-        <v>8.73076923076923</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="H151" t="n">
-        <v>22</v>
-      </c>
-      <c r="I151" t="n">
         <v>0.1363636363636364</v>
       </c>
-      <c r="J151" t="n">
-        <v>0.1363636363636364</v>
-      </c>
-      <c r="K151" t="inlineStr">
+      <c r="I151" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr">
+      <c r="J151" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K151" t="n">
+        <v>53400</v>
       </c>
     </row>
     <row r="152">
@@ -6979,29 +6554,26 @@
         <v>9</v>
       </c>
       <c r="F152" t="n">
-        <v>8.133333333333333</v>
+        <v>60</v>
       </c>
       <c r="G152" t="n">
-        <v>8.709803921568627</v>
+        <v>0.03333333333333333</v>
       </c>
       <c r="H152" t="n">
-        <v>60</v>
-      </c>
-      <c r="I152" t="n">
         <v>0.03333333333333333</v>
       </c>
-      <c r="J152" t="n">
-        <v>0.03333333333333333</v>
-      </c>
-      <c r="K152" t="inlineStr">
+      <c r="I152" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr">
+      <c r="J152" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K152" t="n">
+        <v>116000</v>
       </c>
     </row>
     <row r="153">
@@ -7022,26 +6594,27 @@
       <c r="E153" t="n">
         <v>8.5</v>
       </c>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
+      <c r="F153" t="n">
+        <v>5</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0.4</v>
+      </c>
       <c r="H153" t="n">
-        <v>5</v>
-      </c>
-      <c r="I153" t="n">
         <v>0.4</v>
       </c>
-      <c r="J153" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K153" t="inlineStr">
+      <c r="I153" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr">
+      <c r="J153" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K153" t="n">
+        <v>109000</v>
       </c>
     </row>
     <row r="154">
@@ -7063,29 +6636,26 @@
         <v>8.5</v>
       </c>
       <c r="F154" t="n">
-        <v>5.214285714285714</v>
+        <v>9</v>
       </c>
       <c r="G154" t="n">
-        <v>8</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="H154" t="n">
-        <v>9</v>
-      </c>
-      <c r="I154" t="n">
         <v>0.1111111111111111</v>
       </c>
-      <c r="J154" t="n">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr">
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K154" t="n">
+        <v>215000</v>
       </c>
     </row>
     <row r="155">
@@ -7107,29 +6677,26 @@
         <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>5.189655172413793</v>
+        <v>37</v>
       </c>
       <c r="G155" t="n">
-        <v>1.3</v>
+        <v>0.1891891891891892</v>
       </c>
       <c r="H155" t="n">
-        <v>37</v>
-      </c>
-      <c r="I155" t="n">
-        <v>0.1891891891891892</v>
-      </c>
-      <c r="J155" t="n">
         <v>0.1621621621621622</v>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr">
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K155" t="n">
+        <v>121000</v>
       </c>
     </row>
     <row r="156">
@@ -7151,29 +6718,26 @@
         <v>2.5</v>
       </c>
       <c r="F156" t="n">
-        <v>5.125</v>
+        <v>31</v>
       </c>
       <c r="G156" t="n">
-        <v>3.6875</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="H156" t="n">
-        <v>31</v>
-      </c>
-      <c r="I156" t="n">
         <v>0.7096774193548387</v>
       </c>
-      <c r="J156" t="n">
-        <v>0.7096774193548387</v>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr">
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K156" t="n">
+        <v>105000</v>
       </c>
     </row>
     <row r="157">
@@ -7195,29 +6759,26 @@
         <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>5.364285714285715</v>
+        <v>55</v>
       </c>
       <c r="G157" t="n">
-        <v>2.616279069767442</v>
+        <v>0.2181818181818182</v>
       </c>
       <c r="H157" t="n">
-        <v>55</v>
-      </c>
-      <c r="I157" t="n">
-        <v>0.2181818181818182</v>
-      </c>
-      <c r="J157" t="n">
         <v>0.2</v>
       </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr">
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K157" t="n">
+        <v>679000</v>
       </c>
     </row>
     <row r="158">
@@ -7239,29 +6800,26 @@
         <v>8.5</v>
       </c>
       <c r="F158" t="n">
-        <v>5.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="G158" t="n">
-        <v>8.166666666666666</v>
+        <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>3</v>
-      </c>
-      <c r="I158" t="n">
-        <v>0</v>
-      </c>
-      <c r="J158" t="n">
-        <v>0</v>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
         <is>
           <t>high</t>
         </is>
+      </c>
+      <c r="K158" t="n">
+        <v>677000</v>
       </c>
     </row>
     <row r="159">
@@ -7283,29 +6841,26 @@
         <v>6.5</v>
       </c>
       <c r="F159" t="n">
-        <v>7.172413793103448</v>
+        <v>31</v>
       </c>
       <c r="G159" t="n">
-        <v>5.137931034482759</v>
+        <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>31</v>
-      </c>
-      <c r="I159" t="n">
-        <v>0</v>
-      </c>
-      <c r="J159" t="n">
-        <v>0</v>
-      </c>
-      <c r="K159" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I159" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr">
+      <c r="J159" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K159" t="n">
+        <v>160000</v>
       </c>
     </row>
     <row r="160">
@@ -7327,29 +6882,26 @@
         <v>7</v>
       </c>
       <c r="F160" t="n">
-        <v>6.236842105263158</v>
+        <v>25</v>
       </c>
       <c r="G160" t="n">
-        <v>5.947368421052632</v>
+        <v>0.24</v>
       </c>
       <c r="H160" t="n">
-        <v>25</v>
-      </c>
-      <c r="I160" t="n">
         <v>0.24</v>
       </c>
-      <c r="J160" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K160" t="n">
+        <v>391000</v>
       </c>
     </row>
     <row r="161">
@@ -7371,29 +6923,26 @@
         <v>1.5</v>
       </c>
       <c r="F161" t="n">
-        <v>3.9</v>
+        <v>59</v>
       </c>
       <c r="G161" t="n">
-        <v>3.2</v>
+        <v>0.3220338983050847</v>
       </c>
       <c r="H161" t="n">
-        <v>59</v>
-      </c>
-      <c r="I161" t="n">
-        <v>0.3220338983050847</v>
-      </c>
-      <c r="J161" t="n">
         <v>0.1864406779661017</v>
       </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr">
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K161" t="n">
+        <v>286000</v>
       </c>
     </row>
     <row r="162">
@@ -7415,29 +6964,26 @@
         <v>4.5</v>
       </c>
       <c r="F162" t="n">
-        <v>6.604651162790698</v>
+        <v>60</v>
       </c>
       <c r="G162" t="n">
-        <v>4.111111111111111</v>
+        <v>0.2833333333333333</v>
       </c>
       <c r="H162" t="n">
-        <v>60</v>
-      </c>
-      <c r="I162" t="n">
-        <v>0.2833333333333333</v>
-      </c>
-      <c r="J162" t="n">
         <v>0.25</v>
       </c>
-      <c r="K162" t="inlineStr">
+      <c r="I162" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
+      <c r="J162" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K162" t="n">
+        <v>168000</v>
       </c>
     </row>
     <row r="163">
@@ -7459,29 +7005,26 @@
         <v>1</v>
       </c>
       <c r="F163" t="n">
-        <v>5.3</v>
+        <v>25</v>
       </c>
       <c r="G163" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>25</v>
-      </c>
-      <c r="I163" t="n">
-        <v>0</v>
-      </c>
-      <c r="J163" t="n">
-        <v>0</v>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K163" t="n">
+        <v>340000</v>
       </c>
     </row>
     <row r="164">
@@ -7503,29 +7046,26 @@
         <v>0</v>
       </c>
       <c r="F164" t="n">
-        <v>4.795454545454546</v>
+        <v>40</v>
       </c>
       <c r="G164" t="n">
-        <v>1.327586206896552</v>
+        <v>0.375</v>
       </c>
       <c r="H164" t="n">
-        <v>40</v>
-      </c>
-      <c r="I164" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="J164" t="n">
         <v>0.175</v>
       </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr">
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K164" t="n">
+        <v>1060000</v>
       </c>
     </row>
     <row r="165">
@@ -7538,19 +7078,20 @@
       <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr"/>
+      <c r="F165" t="n">
+        <v>1</v>
+      </c>
+      <c r="G165" t="n">
+        <v>1</v>
+      </c>
       <c r="H165" t="n">
         <v>1</v>
       </c>
-      <c r="I165" t="n">
-        <v>1</v>
-      </c>
-      <c r="J165" t="n">
-        <v>1</v>
-      </c>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="n">
+        <v>161000</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7571,29 +7112,26 @@
         <v>8.5</v>
       </c>
       <c r="F166" t="n">
-        <v>7.25925925925926</v>
+        <v>60</v>
       </c>
       <c r="G166" t="n">
-        <v>7.462962962962963</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="H166" t="n">
-        <v>60</v>
-      </c>
-      <c r="I166" t="n">
-        <v>0.4666666666666667</v>
-      </c>
-      <c r="J166" t="n">
         <v>0.45</v>
       </c>
-      <c r="K166" t="inlineStr">
+      <c r="I166" t="inlineStr">
         <is>
           <t>right</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
+      <c r="J166" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K166" t="n">
+        <v>249000</v>
       </c>
     </row>
     <row r="167">
@@ -7615,29 +7153,26 @@
         <v>6.25</v>
       </c>
       <c r="F167" t="n">
-        <v>4.425</v>
+        <v>24</v>
       </c>
       <c r="G167" t="n">
-        <v>4.238095238095238</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="H167" t="n">
-        <v>24</v>
-      </c>
-      <c r="I167" t="n">
-        <v>0.08333333333333333</v>
-      </c>
-      <c r="J167" t="n">
-        <v>0</v>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K167" t="n">
+        <v>1860000</v>
       </c>
     </row>
     <row r="168">
@@ -7659,29 +7194,26 @@
         <v>1</v>
       </c>
       <c r="F168" t="n">
-        <v>5.25</v>
+        <v>13</v>
       </c>
       <c r="G168" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>13</v>
-      </c>
-      <c r="I168" t="n">
-        <v>0</v>
-      </c>
-      <c r="J168" t="n">
-        <v>0</v>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
         <is>
           <t>moderate</t>
         </is>
+      </c>
+      <c r="K168" t="n">
+        <v>63400</v>
       </c>
     </row>
     <row r="169">
@@ -7703,29 +7235,26 @@
         <v>0</v>
       </c>
       <c r="F169" t="n">
-        <v>4.522727272727272</v>
+        <v>37</v>
       </c>
       <c r="G169" t="n">
-        <v>1.434782608695652</v>
+        <v>0.4054054054054054</v>
       </c>
       <c r="H169" t="n">
-        <v>37</v>
-      </c>
-      <c r="I169" t="n">
-        <v>0.4054054054054054</v>
-      </c>
-      <c r="J169" t="n">
         <v>0.3783783783783784</v>
       </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr">
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K169" t="n">
+        <v>736000</v>
       </c>
     </row>
     <row r="170">
@@ -7747,29 +7276,26 @@
         <v>0</v>
       </c>
       <c r="F170" t="n">
-        <v>4.5</v>
+        <v>60</v>
       </c>
       <c r="G170" t="n">
-        <v>0.3888888888888889</v>
+        <v>0.85</v>
       </c>
       <c r="H170" t="n">
-        <v>60</v>
-      </c>
-      <c r="I170" t="n">
         <v>0.85</v>
       </c>
-      <c r="J170" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr">
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
         <is>
           <t>low</t>
         </is>
+      </c>
+      <c r="K170" t="n">
+        <v>1160000</v>
       </c>
     </row>
   </sheetData>
